--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_BRKBZ-CSTD-2-00-C-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_BRKBZ-CSTD-2-00-C-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\s10035azcfs0534.file.core.windows.net\metersoft\開発用\Toyota\BEV\kse\ryo\FF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE1F671-2C67-4BE5-9287-6232A00DAEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38B753A-32F1-4381-BB0E-239D60EDC5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="17" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="_1AB030_" localSheetId="0" hidden="1">{"A",#N/A,FALSE,"(部)工程別 ";"B",#N/A,FALSE,"(部)工程別 ";"D",#N/A,FALSE,"(部)工程別 "}</definedName>
@@ -76,8 +75,8 @@
     <definedName name="IG">#REF!</definedName>
     <definedName name="K">#REF!</definedName>
     <definedName name="LED">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area">[3]Sheet1!$A$1:$I$233</definedName>
-    <definedName name="_xlnm.Print_Titles">[4]車両仕様!$A$1:$C$65536,[4]車両仕様!$A$3:$IV$4</definedName>
+    <definedName name="_xlnm.Print_Area">[2]Sheet1!$A$1:$I$233</definedName>
+    <definedName name="_xlnm.Print_Titles">[3]車両仕様!$A$1:$C$65536,[3]車両仕様!$A$3:$IV$4</definedName>
     <definedName name="ｓ">#REF!</definedName>
     <definedName name="Sheet_dspmaincfg_Top">#REF!</definedName>
     <definedName name="Sheet_ユーザーカスタマイズ手順_Top">#REF!</definedName>
@@ -193,16 +192,16 @@
     <definedName name="愛" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="開発費" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"96下820";#N/A,#N/A,FALSE,"96下826";#N/A,#N/A,FALSE,"96下827";#N/A,#N/A,FALSE,"96下828";#N/A,#N/A,FALSE,"96下861";#N/A,#N/A,FALSE,"96下862"}</definedName>
     <definedName name="開発費" hidden="1">{#N/A,#N/A,FALSE,"96下820";#N/A,#N/A,FALSE,"96下826";#N/A,#N/A,FALSE,"96下827";#N/A,#N/A,FALSE,"96下828";#N/A,#N/A,FALSE,"96下861";#N/A,#N/A,FALSE,"96下862"}</definedName>
-    <definedName name="関数名_確定_BON">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_IGOFF">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_IGON">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_WKUP">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_0">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_1">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_2">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_3">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_4">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_定期">'[5]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_BON">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_IGOFF">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_IGON">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_WKUP">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_0">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_1">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_2">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_3">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_4">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_定期">'[4]Config - dspmgr'!#REF!</definedName>
     <definedName name="金型共通化" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="金型共通化" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="金型共通化２" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
@@ -5348,6 +5347,63 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5381,16 +5437,37 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5435,31 +5512,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5518,63 +5574,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6665,22 +6664,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>49293</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>8400</xdr:rowOff>
+      <xdr:colOff>27255</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>364116</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>82987</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>170605</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CC266AC-6CA1-49C8-8DF7-BEF5BE232E21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BD344E3-1606-F19B-1F62-F0C6FDF72B5B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6696,12 +6695,17 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="665466" y="39492734"/>
-          <a:ext cx="13648796" cy="1356226"/>
+          <a:off x="707612" y="28112358"/>
+          <a:ext cx="13865638" cy="7069426"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -6709,22 +6713,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>98587</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>45139</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>149682</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>823726</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>47666</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>421821</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>114852</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98BF3F20-D774-4B17-91C8-DFAE98A08B26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED95B404-7C77-D19A-2897-5BC616A2F7AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6740,12 +6744,66 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="714760" y="31519230"/>
-          <a:ext cx="11483510" cy="7371951"/>
+          <a:off x="680357" y="25785539"/>
+          <a:ext cx="15144750" cy="1380313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>68077</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>153760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>2010387</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>122463</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC057F2E-CAE0-CFAD-1534-EA04B188AFCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="748434" y="16768081"/>
+          <a:ext cx="13821346" cy="8282668"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -6753,13 +6811,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>386570</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>2299</xdr:rowOff>
+      <xdr:colOff>996306</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1577479</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>96878</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>136820</xdr:rowOff>
     </xdr:to>
@@ -6776,8 +6834,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7521847" y="32597825"/>
-          <a:ext cx="1190909" cy="6222306"/>
+          <a:off x="8874842" y="17961429"/>
+          <a:ext cx="1441000" cy="6926784"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6818,16 +6876,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1587744</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295062</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>119079</xdr:rowOff>
+      <xdr:rowOff>37436</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1196570</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>1804</xdr:rowOff>
+      <xdr:colOff>2244316</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>97053</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6842,8 +6900,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8723021" y="32073785"/>
-          <a:ext cx="1728460" cy="363339"/>
+          <a:off x="10514026" y="17359329"/>
+          <a:ext cx="1949254" cy="413403"/>
         </a:xfrm>
         <a:prstGeom prst="borderCallout1">
           <a:avLst>
@@ -6924,15 +6982,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1060216</xdr:colOff>
+      <xdr:colOff>1129439</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>65461</xdr:rowOff>
+      <xdr:rowOff>112821</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>651199</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>46016</xdr:rowOff>
+      <xdr:colOff>663619</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>175550</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6947,8 +7005,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10315127" y="39870205"/>
-          <a:ext cx="1710616" cy="941784"/>
+          <a:off x="11348403" y="26102464"/>
+          <a:ext cx="1874609" cy="947193"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7150,15 +7208,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1448097</xdr:colOff>
+      <xdr:colOff>1576016</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>42097</xdr:rowOff>
+      <xdr:rowOff>103005</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1042629</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>21369</xdr:rowOff>
+      <xdr:colOff>1132422</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>164567</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7173,8 +7231,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8583374" y="39846841"/>
-          <a:ext cx="1714166" cy="940501"/>
+          <a:off x="9454552" y="26092648"/>
+          <a:ext cx="1896834" cy="946026"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7246,8 +7304,8 @@
           <a:avLst>
             <a:gd name="adj1" fmla="val 55643"/>
             <a:gd name="adj2" fmla="val 29"/>
-            <a:gd name="adj3" fmla="val 258633"/>
-            <a:gd name="adj4" fmla="val -88771"/>
+            <a:gd name="adj3" fmla="val 256042"/>
+            <a:gd name="adj4" fmla="val -63905"/>
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
@@ -7319,15 +7377,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>115851</xdr:colOff>
+      <xdr:colOff>115850</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>140606</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>749787</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>131823</xdr:rowOff>
+      <xdr:colOff>1864177</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7342,8 +7400,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="732024" y="35299409"/>
-          <a:ext cx="11392307" cy="952447"/>
+          <a:off x="796207" y="21000356"/>
+          <a:ext cx="13627363" cy="1124858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7391,7 +7449,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>737463</xdr:colOff>
+      <xdr:colOff>1864178</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>144904</xdr:rowOff>
     </xdr:to>
@@ -7408,8 +7466,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="678725" y="38344174"/>
-          <a:ext cx="11433282" cy="484041"/>
+          <a:off x="742909" y="24362192"/>
+          <a:ext cx="13680662" cy="534105"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7524,7 +7582,7 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>MET-C_BRKBZ-CSTD-2-00-B-C0.xlsm</a:t>
+            <a:t>MET-C_BRKBZ-CSTD-2-00-C-C0</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
             <a:solidFill>
@@ -7541,7 +7599,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>737463</xdr:colOff>
+      <xdr:colOff>1864178</xdr:colOff>
       <xdr:row>94</xdr:row>
       <xdr:rowOff>132061</xdr:rowOff>
     </xdr:from>
@@ -7567,8 +7625,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="13296856" y="20461132"/>
-          <a:ext cx="3852526" cy="4168113"/>
+          <a:off x="14423571" y="20461132"/>
+          <a:ext cx="2725811" cy="4168113"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -7598,280 +7656,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>33045</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>246324</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>173723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>549099</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>153470</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B1FAA2B-B186-4098-A733-ADA8AA5268C7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="616173" y="24297918"/>
-          <a:ext cx="11307470" cy="6208208"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>209500</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>150443</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>920547</xdr:colOff>
-      <xdr:row>177</xdr:row>
-      <xdr:rowOff>44423</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="図 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67564B10-957B-4C8D-8582-2DA468FB24A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="825673" y="41717440"/>
-          <a:ext cx="11469418" cy="6302175"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>234146</xdr:colOff>
-      <xdr:row>179</xdr:row>
-      <xdr:rowOff>119309</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>964246</xdr:colOff>
-      <xdr:row>214</xdr:row>
-      <xdr:rowOff>115851</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FA5780-F78F-4CC6-ADEE-849C5E976C85}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="850319" y="48414910"/>
-          <a:ext cx="11488471" cy="5603712"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>345057</xdr:colOff>
-      <xdr:row>216</xdr:row>
-      <xdr:rowOff>83637</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1056104</xdr:colOff>
-      <xdr:row>251</xdr:row>
-      <xdr:rowOff>24317</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{317A9364-481E-43D0-860E-5910FB8F003A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="961230" y="54306817"/>
-          <a:ext cx="11469418" cy="5547850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>480616</xdr:colOff>
-      <xdr:row>253</xdr:row>
-      <xdr:rowOff>60286</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1191663</xdr:colOff>
-      <xdr:row>300</xdr:row>
-      <xdr:rowOff>119330</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="図 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3333FB24-AEE6-45EE-A85E-3E38285799BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1096789" y="60211046"/>
-          <a:ext cx="11469418" cy="7588673"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>455969</xdr:colOff>
-      <xdr:row>303</xdr:row>
-      <xdr:rowOff>69367</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1262279</xdr:colOff>
-      <xdr:row>348</xdr:row>
-      <xdr:rowOff>41783</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04993083-135B-43C7-A5E0-638FE504D0B5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1072142" y="68230370"/>
-          <a:ext cx="11564681" cy="7181634"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1402931</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>105688</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>63240</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>90454</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>137468</xdr:rowOff>
+      <xdr:rowOff>28611</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7886,8 +7680,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12777475" y="42633914"/>
-          <a:ext cx="1987641" cy="672601"/>
+          <a:off x="14819574" y="28993652"/>
+          <a:ext cx="2334237" cy="739352"/>
         </a:xfrm>
         <a:prstGeom prst="borderCallout1">
           <a:avLst>
@@ -7952,6 +7746,300 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>148470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E64DB9E4-08B8-D958-B87F-B371AE892F09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="8831035"/>
+          <a:ext cx="13892894" cy="7047292"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>176892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>154565</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8224DF3B-77ED-489D-F2D5-89FD781B96F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="35541856"/>
+          <a:ext cx="13892893" cy="6168923"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1986643</xdr:colOff>
+      <xdr:row>250</xdr:row>
+      <xdr:rowOff>155743</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D8270F-70C8-81DB-3147-7233AE55CDE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="41910000"/>
+          <a:ext cx="13865679" cy="6170100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>253</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1986643</xdr:colOff>
+      <xdr:row>289</xdr:row>
+      <xdr:rowOff>83780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29FCF581-AF25-FABF-A9CB-8F42A78D269F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680358" y="48455036"/>
+          <a:ext cx="13865678" cy="6451923"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>289</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>127234</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11074D52-937B-A662-2561-264D21C94F97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="54877607"/>
+          <a:ext cx="13879286" cy="3610663"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>311</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:row>346</xdr:row>
+      <xdr:rowOff>121394</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{501D9226-8B69-A771-8CEC-8E3B5E32974F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="58714821"/>
+          <a:ext cx="13879286" cy="6312644"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -8265,56 +8353,6 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="表紙（承認欄）"/>
-      <sheetName val="変更履歴"/>
-      <sheetName val="要件分析, ソフト分析"/>
-      <sheetName val="課題リスト"/>
-      <sheetName val="MAPPING(Featureのみ)"/>
-      <sheetName val="Evidence(Featureのみ)"/>
-      <sheetName val="MAPPING"/>
-      <sheetName val="param"/>
-      <sheetName val="Evidence"/>
-      <sheetName val="2. 仕様差分の確認結果(for traceability)"/>
-      <sheetName val="2. 仕様差分の確認結果(for visibility)"/>
-      <sheetName val="2-1.要件分析_ストラテジ"/>
-      <sheetName val="3. 関連仕様の確認結果_詳細"/>
-      <sheetName val="設計・評価方針(仕様変化点_設計方針から抽出)"/>
-      <sheetName val="4. ソフト変更方法の詳細"/>
-      <sheetName val="ブロック図(概要)"/>
-      <sheetName val="留意点に対する設計結果_詳細"/>
-      <sheetName val="5.ソフト影響箇所の確認_詳細"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="GVIF1"/>
@@ -8428,11 +8466,11 @@
       <sheetName val="PullDown"/>
       <sheetName val="分类数据"/>
       <sheetName val="引言"/>
-      <sheetName val="#REF!"/>
-      <sheetName val="コマンド認識, DTMF"/>
       <sheetName val="県別ﾏﾙﾁ"/>
       <sheetName val="車両仕様"/>
       <sheetName val="FMEA記載方法"/>
+      <sheetName val="#REF!"/>
+      <sheetName val="コマンド認識, DTMF"/>
       <sheetName val="基本情報"/>
       <sheetName val="リスク"/>
       <sheetName val="改訂履歴"/>
@@ -8495,6 +8533,14 @@
       <sheetName val="場所指定地図"/>
       <sheetName val="ﾕｰｻﾞｰ設定"/>
       <sheetName val="入力"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="メイン"/>
+      <sheetName val="一覧１"/>
+      <sheetName val="No.31"/>
+      <sheetName val="Cover"/>
+      <sheetName val="LS1 and LS2"/>
+      <sheetName val="00"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -8682,12 +8728,20 @@
       <sheetData sheetId="176" refreshError="1"/>
       <sheetData sheetId="177" refreshError="1"/>
       <sheetData sheetId="178" refreshError="1"/>
+      <sheetData sheetId="179" refreshError="1"/>
+      <sheetData sheetId="180" refreshError="1"/>
+      <sheetData sheetId="181" refreshError="1"/>
+      <sheetData sheetId="182" refreshError="1"/>
+      <sheetData sheetId="183" refreshError="1"/>
+      <sheetData sheetId="184" refreshError="1"/>
+      <sheetData sheetId="185" refreshError="1"/>
+      <sheetData sheetId="186" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -10006,19 +10060,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
-      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="C-55227AB"/>
+      <sheetName val="Data Definition"/>
+      <sheetName val="FC_まとめる"/>
       <sheetName val="vocabulary"/>
       <sheetName val="Calibration"/>
       <sheetName val="CVBS"/>
       <sheetName val="RGB"/>
-      <sheetName val="option"/>
-      <sheetName val="課題管理"/>
-      <sheetName val="C-55227AB"/>
-      <sheetName val="Data Definition"/>
-      <sheetName val="FC_まとめる"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="入力規則"/>
+      <sheetName val="課題管理"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="option"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
       <sheetName val="OpenIssueList"/>
@@ -10033,6 +10086,7 @@
       <sheetName val="リソーセス算出"/>
       <sheetName val="定義"/>
       <sheetName val="キーデコード処理"/>
+      <sheetName val="入力規則"/>
       <sheetName val="目次"/>
       <sheetName val="試験要領4頁"/>
       <sheetName val="FAC OVERHEAD"/>
@@ -10060,16 +10114,6 @@
       <sheetName val="DONEM"/>
       <sheetName val="TP（SYS→NAVI）"/>
       <sheetName val="RAM_FMEA_CS（FMEA記載方法）"/>
-      <sheetName val="XSSマイコン依存部 (基本設定)"/>
-      <sheetName val="ハード"/>
-      <sheetName val="DataList"/>
-      <sheetName val="FMEA記載方法"/>
-      <sheetName val="計画"/>
-      <sheetName val="字段定义"/>
-      <sheetName val="rom map"/>
-      <sheetName val="議事・勧告一覧"/>
-      <sheetName val="excludedmodels"/>
-      <sheetName val="#入力規則"/>
       <sheetName val="测试计划"/>
       <sheetName val="memReg(2)"/>
       <sheetName val="info"/>
@@ -10106,6 +10150,16 @@
       <sheetName val="TAGLユニットリスト"/>
       <sheetName val="材料費明細(M)"/>
       <sheetName val="入力LIST"/>
+      <sheetName val="FMEA記載方法"/>
+      <sheetName val="XSSマイコン依存部 (基本設定)"/>
+      <sheetName val="ハード"/>
+      <sheetName val="DataList"/>
+      <sheetName val="計画"/>
+      <sheetName val="字段定义"/>
+      <sheetName val="rom map"/>
+      <sheetName val="議事・勧告一覧"/>
+      <sheetName val="excludedmodels"/>
+      <sheetName val="#入力規則"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
       <sheetName val="リストデータ"/>
@@ -11855,9 +11909,6 @@
       <sheetName val="進捗"/>
       <sheetName val="印刷"/>
       <sheetName val="試験項目_R3小"/>
-      <sheetName val="Config_by_Program"/>
-      <sheetName val="DIAG_cfg_setting"/>
-      <sheetName val="AUBISTConfigurator_AssistTool"/>
       <sheetName val="Toggle_Duplicate_Highlighting"/>
       <sheetName val="M_ACCOUNT"/>
       <sheetName val="自販市場別"/>
@@ -13956,6 +14007,31 @@
       <sheetName val="車両仕様__x005f_x005f_x005f_x005F_2"/>
       <sheetName val="Process"/>
       <sheetName val="BOM"/>
+      <sheetName val="Config_by_Program"/>
+      <sheetName val="DIAG_cfg_setting"/>
+      <sheetName val="AUBISTConfigurator_AssistTool"/>
+      <sheetName val="項目"/>
+      <sheetName val="100万未満"/>
+      <sheetName val="301-01.起動"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Func.Share"/>
+      <sheetName val="場所指定地図"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="Func.Share(DR-0320)"/>
+      <sheetName val="状況"/>
+      <sheetName val="ドメイン"/>
+      <sheetName val="tda30al"/>
+      <sheetName val="ﾃﾞｰﾀﾍﾞｰｽ"/>
+      <sheetName val="需求与代码对比"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="メイン"/>
+      <sheetName val="一覧１"/>
+      <sheetName val="入力候補"/>
+      <sheetName val="HMI-004_Screen（old）"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -18657,14 +18733,14 @@
       <sheetData sheetId="1312" refreshError="1"/>
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
-      <sheetData sheetId="1315" refreshError="1"/>
+      <sheetData sheetId="1315"/>
       <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322"/>
+      <sheetData sheetId="1322" refreshError="1"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -18735,22 +18811,22 @@
       <sheetData sheetId="1390" refreshError="1"/>
       <sheetData sheetId="1391" refreshError="1"/>
       <sheetData sheetId="1392" refreshError="1"/>
-      <sheetData sheetId="1393" refreshError="1"/>
-      <sheetData sheetId="1394" refreshError="1"/>
-      <sheetData sheetId="1395" refreshError="1"/>
+      <sheetData sheetId="1393"/>
+      <sheetData sheetId="1394"/>
+      <sheetData sheetId="1395"/>
       <sheetData sheetId="1396" refreshError="1"/>
-      <sheetData sheetId="1397" refreshError="1"/>
-      <sheetData sheetId="1398" refreshError="1"/>
+      <sheetData sheetId="1397"/>
+      <sheetData sheetId="1398"/>
       <sheetData sheetId="1399" refreshError="1"/>
       <sheetData sheetId="1400" refreshError="1"/>
       <sheetData sheetId="1401" refreshError="1"/>
       <sheetData sheetId="1402" refreshError="1"/>
-      <sheetData sheetId="1403"/>
-      <sheetData sheetId="1404"/>
-      <sheetData sheetId="1405"/>
+      <sheetData sheetId="1403" refreshError="1"/>
+      <sheetData sheetId="1404" refreshError="1"/>
+      <sheetData sheetId="1405" refreshError="1"/>
       <sheetData sheetId="1406" refreshError="1"/>
-      <sheetData sheetId="1407"/>
-      <sheetData sheetId="1408"/>
+      <sheetData sheetId="1407" refreshError="1"/>
+      <sheetData sheetId="1408" refreshError="1"/>
       <sheetData sheetId="1409" refreshError="1"/>
       <sheetData sheetId="1410" refreshError="1"/>
       <sheetData sheetId="1411" refreshError="1"/>
@@ -21758,17 +21834,17 @@
       <sheetData sheetId="3161" refreshError="1"/>
       <sheetData sheetId="3162" refreshError="1"/>
       <sheetData sheetId="3163" refreshError="1"/>
-      <sheetData sheetId="3164" refreshError="1"/>
+      <sheetData sheetId="3164"/>
       <sheetData sheetId="3165" refreshError="1"/>
       <sheetData sheetId="3166" refreshError="1"/>
-      <sheetData sheetId="3167"/>
+      <sheetData sheetId="3167" refreshError="1"/>
       <sheetData sheetId="3168" refreshError="1"/>
       <sheetData sheetId="3169" refreshError="1"/>
       <sheetData sheetId="3170" refreshError="1"/>
       <sheetData sheetId="3171" refreshError="1"/>
-      <sheetData sheetId="3172" refreshError="1"/>
-      <sheetData sheetId="3173" refreshError="1"/>
-      <sheetData sheetId="3174" refreshError="1"/>
+      <sheetData sheetId="3172"/>
+      <sheetData sheetId="3173"/>
+      <sheetData sheetId="3174"/>
       <sheetData sheetId="3175"/>
       <sheetData sheetId="3176"/>
       <sheetData sheetId="3177"/>
@@ -22050,19 +22126,19 @@
       <sheetData sheetId="3453"/>
       <sheetData sheetId="3454"/>
       <sheetData sheetId="3455"/>
-      <sheetData sheetId="3456"/>
+      <sheetData sheetId="3456" refreshError="1"/>
       <sheetData sheetId="3457"/>
       <sheetData sheetId="3458"/>
-      <sheetData sheetId="3459" refreshError="1"/>
+      <sheetData sheetId="3459">
+        <row r="1">
+          <cell r="A1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3460"/>
       <sheetData sheetId="3461"/>
-      <sheetData sheetId="3462">
-        <row r="1">
-          <cell r="A1">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3462"/>
       <sheetData sheetId="3463"/>
       <sheetData sheetId="3464"/>
       <sheetData sheetId="3465"/>
@@ -22217,40 +22293,40 @@
       <sheetData sheetId="3614"/>
       <sheetData sheetId="3615"/>
       <sheetData sheetId="3616"/>
-      <sheetData sheetId="3617"/>
+      <sheetData sheetId="3617">
+        <row r="1">
+          <cell r="A1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3618"/>
       <sheetData sheetId="3619"/>
-      <sheetData sheetId="3620">
-        <row r="1">
-          <cell r="A1">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3620"/>
       <sheetData sheetId="3621"/>
       <sheetData sheetId="3622"/>
       <sheetData sheetId="3623"/>
       <sheetData sheetId="3624"/>
       <sheetData sheetId="3625"/>
-      <sheetData sheetId="3626"/>
+      <sheetData sheetId="3626">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3627"/>
       <sheetData sheetId="3628"/>
       <sheetData sheetId="3629">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3630"/>
       <sheetData sheetId="3631"/>
-      <sheetData sheetId="3632">
-        <row r="1">
-          <cell r="A1">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3632"/>
       <sheetData sheetId="3633"/>
       <sheetData sheetId="3634"/>
       <sheetData sheetId="3635"/>
@@ -22375,16 +22451,16 @@
       <sheetData sheetId="3754"/>
       <sheetData sheetId="3755"/>
       <sheetData sheetId="3756"/>
-      <sheetData sheetId="3757"/>
+      <sheetData sheetId="3757">
+        <row r="1">
+          <cell r="A1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3758"/>
       <sheetData sheetId="3759"/>
-      <sheetData sheetId="3760">
-        <row r="1">
-          <cell r="A1">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3760"/>
       <sheetData sheetId="3761"/>
       <sheetData sheetId="3762"/>
       <sheetData sheetId="3763"/>
@@ -22403,16 +22479,16 @@
       <sheetData sheetId="3776"/>
       <sheetData sheetId="3777"/>
       <sheetData sheetId="3778"/>
-      <sheetData sheetId="3779"/>
+      <sheetData sheetId="3779">
+        <row r="1">
+          <cell r="A1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3780"/>
       <sheetData sheetId="3781"/>
-      <sheetData sheetId="3782">
-        <row r="1">
-          <cell r="A1">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3782"/>
       <sheetData sheetId="3783"/>
       <sheetData sheetId="3784"/>
       <sheetData sheetId="3785"/>
@@ -23828,9 +23904,9 @@
       <sheetData sheetId="5195"/>
       <sheetData sheetId="5196"/>
       <sheetData sheetId="5197"/>
-      <sheetData sheetId="5198"/>
-      <sheetData sheetId="5199"/>
-      <sheetData sheetId="5200"/>
+      <sheetData sheetId="5198" refreshError="1"/>
+      <sheetData sheetId="5199" refreshError="1"/>
+      <sheetData sheetId="5200" refreshError="1"/>
       <sheetData sheetId="5201" refreshError="1"/>
       <sheetData sheetId="5202" refreshError="1"/>
       <sheetData sheetId="5203" refreshError="1"/>
@@ -23846,23 +23922,23 @@
       <sheetData sheetId="5213" refreshError="1"/>
       <sheetData sheetId="5214" refreshError="1"/>
       <sheetData sheetId="5215" refreshError="1"/>
-      <sheetData sheetId="5216" refreshError="1"/>
-      <sheetData sheetId="5217" refreshError="1"/>
-      <sheetData sheetId="5218" refreshError="1"/>
+      <sheetData sheetId="5216"/>
+      <sheetData sheetId="5217"/>
+      <sheetData sheetId="5218"/>
       <sheetData sheetId="5219"/>
       <sheetData sheetId="5220"/>
       <sheetData sheetId="5221"/>
       <sheetData sheetId="5222"/>
       <sheetData sheetId="5223"/>
-      <sheetData sheetId="5224"/>
-      <sheetData sheetId="5225"/>
-      <sheetData sheetId="5226"/>
+      <sheetData sheetId="5224" refreshError="1"/>
+      <sheetData sheetId="5225" refreshError="1"/>
+      <sheetData sheetId="5226" refreshError="1"/>
       <sheetData sheetId="5227" refreshError="1"/>
       <sheetData sheetId="5228" refreshError="1"/>
       <sheetData sheetId="5229" refreshError="1"/>
-      <sheetData sheetId="5230" refreshError="1"/>
-      <sheetData sheetId="5231" refreshError="1"/>
-      <sheetData sheetId="5232" refreshError="1"/>
+      <sheetData sheetId="5230"/>
+      <sheetData sheetId="5231"/>
+      <sheetData sheetId="5232"/>
       <sheetData sheetId="5233"/>
       <sheetData sheetId="5234"/>
       <sheetData sheetId="5235"/>
@@ -23879,28 +23955,50 @@
       <sheetData sheetId="5246"/>
       <sheetData sheetId="5247"/>
       <sheetData sheetId="5248"/>
-      <sheetData sheetId="5249"/>
-      <sheetData sheetId="5250"/>
+      <sheetData sheetId="5249" refreshError="1"/>
+      <sheetData sheetId="5250" refreshError="1"/>
       <sheetData sheetId="5251"/>
-      <sheetData sheetId="5252" refreshError="1"/>
-      <sheetData sheetId="5253" refreshError="1"/>
+      <sheetData sheetId="5252"/>
+      <sheetData sheetId="5253"/>
       <sheetData sheetId="5254"/>
       <sheetData sheetId="5255"/>
       <sheetData sheetId="5256"/>
       <sheetData sheetId="5257"/>
       <sheetData sheetId="5258"/>
       <sheetData sheetId="5259"/>
-      <sheetData sheetId="5260"/>
-      <sheetData sheetId="5261"/>
-      <sheetData sheetId="5262"/>
+      <sheetData sheetId="5260" refreshError="1"/>
+      <sheetData sheetId="5261" refreshError="1"/>
+      <sheetData sheetId="5262" refreshError="1"/>
       <sheetData sheetId="5263" refreshError="1"/>
       <sheetData sheetId="5264" refreshError="1"/>
+      <sheetData sheetId="5265" refreshError="1"/>
+      <sheetData sheetId="5266" refreshError="1"/>
+      <sheetData sheetId="5267" refreshError="1"/>
+      <sheetData sheetId="5268" refreshError="1"/>
+      <sheetData sheetId="5269" refreshError="1"/>
+      <sheetData sheetId="5270" refreshError="1"/>
+      <sheetData sheetId="5271" refreshError="1"/>
+      <sheetData sheetId="5272" refreshError="1"/>
+      <sheetData sheetId="5273" refreshError="1"/>
+      <sheetData sheetId="5274" refreshError="1"/>
+      <sheetData sheetId="5275" refreshError="1"/>
+      <sheetData sheetId="5276"/>
+      <sheetData sheetId="5277" refreshError="1"/>
+      <sheetData sheetId="5278" refreshError="1"/>
+      <sheetData sheetId="5279" refreshError="1"/>
+      <sheetData sheetId="5280" refreshError="1"/>
+      <sheetData sheetId="5281" refreshError="1"/>
+      <sheetData sheetId="5282" refreshError="1"/>
+      <sheetData sheetId="5283" refreshError="1"/>
+      <sheetData sheetId="5284" refreshError="1"/>
+      <sheetData sheetId="5285" refreshError="1"/>
+      <sheetData sheetId="5286"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -23993,13 +24091,13 @@
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="Navigation"/>
       <sheetName val="Cover"/>
       <sheetName val="DataList"/>
@@ -24049,6 +24147,14 @@
       <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
       <sheetName val="Setting_Check"/>
       <sheetName val="用語集"/>
+      <sheetName val="工数ｺｰﾄﾞﾌﾟﾙﾀﾞｳﾝﾘｽﾄ"/>
+      <sheetName val="NAVI"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="macro1"/>
+      <sheetName val="発見した問題点"/>
+      <sheetName val="★EngType"/>
+      <sheetName val="★rom map_DevelopVarSel"/>
+      <sheetName val="★rom map_EngType"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -24196,6 +24302,14 @@
       <sheetData sheetId="142" refreshError="1"/>
       <sheetData sheetId="143" refreshError="1"/>
       <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -24492,10 +24606,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.26953125" style="291" customWidth="1"/>
-    <col min="53" max="16384" width="8.81640625" style="291"/>
+    <col min="1" max="52" width="2.25" style="232" customWidth="1"/>
+    <col min="53" max="16384" width="8.875" style="232"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -24508,12 +24622,12 @@
     <row r="8" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="9" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="10" spans="6:20" ht="13.15" customHeight="1">
-      <c r="F10" s="292"/>
+      <c r="F10" s="233"/>
     </row>
     <row r="11" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="12" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="13" spans="6:20" ht="13.15" customHeight="1">
-      <c r="T13" s="293" t="str">
+      <c r="T13" s="234" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("[",CELL("filename",A1))+1,FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-1)</f>
         <v>alert_C_BRKBZ-CSTD-2-00-C-C0.xlsx</v>
       </c>
@@ -24537,20 +24651,20 @@
     <row r="30" spans="3:22" ht="13.15" customHeight="1"/>
     <row r="31" spans="3:22" ht="13.15" customHeight="1"/>
     <row r="32" spans="3:22" ht="13.15" customHeight="1">
-      <c r="C32" s="294"/>
-      <c r="V32" s="294"/>
+      <c r="C32" s="235"/>
+      <c r="V32" s="235"/>
     </row>
     <row r="33" spans="3:39" ht="13.15" customHeight="1">
-      <c r="M33" s="295"/>
-      <c r="N33" s="295"/>
-      <c r="O33" s="295"/>
-      <c r="P33" s="295"/>
-      <c r="Q33" s="295"/>
-      <c r="AF33" s="295"/>
-      <c r="AG33" s="295"/>
-      <c r="AH33" s="295"/>
-      <c r="AI33" s="295"/>
-      <c r="AJ33" s="295"/>
+      <c r="M33" s="236"/>
+      <c r="N33" s="236"/>
+      <c r="O33" s="236"/>
+      <c r="P33" s="236"/>
+      <c r="Q33" s="236"/>
+      <c r="AF33" s="236"/>
+      <c r="AG33" s="236"/>
+      <c r="AH33" s="236"/>
+      <c r="AI33" s="236"/>
+      <c r="AJ33" s="236"/>
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="133" t="s">
@@ -24558,354 +24672,354 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="296" t="s">
+      <c r="Y35" s="248" t="s">
         <v>304</v>
       </c>
-      <c r="Z35" s="297"/>
-      <c r="AA35" s="297"/>
-      <c r="AB35" s="297"/>
-      <c r="AC35" s="298"/>
-      <c r="AD35" s="296" t="s">
+      <c r="Z35" s="249"/>
+      <c r="AA35" s="249"/>
+      <c r="AB35" s="249"/>
+      <c r="AC35" s="250"/>
+      <c r="AD35" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="AE35" s="297"/>
-      <c r="AF35" s="297"/>
-      <c r="AG35" s="297"/>
-      <c r="AH35" s="298"/>
-      <c r="AI35" s="296" t="s">
+      <c r="AE35" s="249"/>
+      <c r="AF35" s="249"/>
+      <c r="AG35" s="249"/>
+      <c r="AH35" s="250"/>
+      <c r="AI35" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="AJ35" s="297"/>
-      <c r="AK35" s="297"/>
-      <c r="AL35" s="297"/>
-      <c r="AM35" s="298"/>
+      <c r="AJ35" s="249"/>
+      <c r="AK35" s="249"/>
+      <c r="AL35" s="249"/>
+      <c r="AM35" s="250"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
-      <c r="D36" s="295"/>
-      <c r="E36" s="299"/>
-      <c r="F36" s="295"/>
-      <c r="G36" s="295"/>
-      <c r="I36" s="295"/>
-      <c r="J36" s="299"/>
-      <c r="K36" s="295"/>
-      <c r="L36" s="295"/>
-      <c r="M36" s="295"/>
-      <c r="N36" s="295"/>
-      <c r="O36" s="299"/>
-      <c r="P36" s="295"/>
-      <c r="Q36" s="295"/>
-      <c r="W36" s="295"/>
-      <c r="X36" s="299"/>
-      <c r="Y36" s="300"/>
-      <c r="Z36" s="301"/>
-      <c r="AA36" s="301"/>
-      <c r="AB36" s="301"/>
-      <c r="AC36" s="302"/>
-      <c r="AD36" s="300"/>
-      <c r="AE36" s="301"/>
-      <c r="AF36" s="301"/>
-      <c r="AG36" s="301"/>
-      <c r="AH36" s="302"/>
-      <c r="AI36" s="300"/>
-      <c r="AJ36" s="301"/>
-      <c r="AK36" s="301"/>
-      <c r="AL36" s="301"/>
-      <c r="AM36" s="302"/>
+      <c r="D36" s="236"/>
+      <c r="E36" s="237"/>
+      <c r="F36" s="236"/>
+      <c r="G36" s="236"/>
+      <c r="I36" s="236"/>
+      <c r="J36" s="237"/>
+      <c r="K36" s="236"/>
+      <c r="L36" s="236"/>
+      <c r="M36" s="236"/>
+      <c r="N36" s="236"/>
+      <c r="O36" s="237"/>
+      <c r="P36" s="236"/>
+      <c r="Q36" s="236"/>
+      <c r="W36" s="236"/>
+      <c r="X36" s="237"/>
+      <c r="Y36" s="238"/>
+      <c r="Z36" s="239"/>
+      <c r="AA36" s="239"/>
+      <c r="AB36" s="239"/>
+      <c r="AC36" s="240"/>
+      <c r="AD36" s="238"/>
+      <c r="AE36" s="239"/>
+      <c r="AF36" s="239"/>
+      <c r="AG36" s="239"/>
+      <c r="AH36" s="240"/>
+      <c r="AI36" s="238"/>
+      <c r="AJ36" s="239"/>
+      <c r="AK36" s="239"/>
+      <c r="AL36" s="239"/>
+      <c r="AM36" s="240"/>
     </row>
     <row r="37" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y37" s="303"/>
-      <c r="AC37" s="304"/>
-      <c r="AD37" s="303"/>
-      <c r="AH37" s="304"/>
-      <c r="AI37" s="303"/>
-      <c r="AM37" s="304"/>
+      <c r="Y37" s="241"/>
+      <c r="AC37" s="242"/>
+      <c r="AD37" s="241"/>
+      <c r="AH37" s="242"/>
+      <c r="AI37" s="241"/>
+      <c r="AM37" s="242"/>
     </row>
     <row r="38" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y38" s="303"/>
-      <c r="Z38" s="295"/>
-      <c r="AA38" s="299" t="s">
+      <c r="Y38" s="241"/>
+      <c r="Z38" s="236"/>
+      <c r="AA38" s="237" t="s">
         <v>307</v>
       </c>
-      <c r="AB38" s="295"/>
-      <c r="AC38" s="305"/>
-      <c r="AD38" s="303"/>
-      <c r="AE38" s="295"/>
-      <c r="AF38" s="299" t="s">
+      <c r="AB38" s="236"/>
+      <c r="AC38" s="243"/>
+      <c r="AD38" s="241"/>
+      <c r="AE38" s="236"/>
+      <c r="AF38" s="237" t="s">
         <v>308</v>
       </c>
-      <c r="AG38" s="295"/>
-      <c r="AH38" s="305"/>
-      <c r="AI38" s="306"/>
-      <c r="AJ38" s="295"/>
-      <c r="AK38" s="299" t="s">
+      <c r="AG38" s="236"/>
+      <c r="AH38" s="243"/>
+      <c r="AI38" s="244"/>
+      <c r="AJ38" s="236"/>
+      <c r="AK38" s="237" t="s">
         <v>309</v>
       </c>
-      <c r="AL38" s="295"/>
-      <c r="AM38" s="305"/>
+      <c r="AL38" s="236"/>
+      <c r="AM38" s="243"/>
     </row>
     <row r="39" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y39" s="303"/>
-      <c r="AC39" s="304"/>
-      <c r="AD39" s="303"/>
-      <c r="AH39" s="304"/>
-      <c r="AI39" s="303"/>
-      <c r="AM39" s="304"/>
+      <c r="Y39" s="241"/>
+      <c r="AC39" s="242"/>
+      <c r="AD39" s="241"/>
+      <c r="AH39" s="242"/>
+      <c r="AI39" s="241"/>
+      <c r="AM39" s="242"/>
     </row>
     <row r="40" spans="3:39" ht="13.15" customHeight="1">
-      <c r="C40" s="294"/>
-      <c r="V40" s="294"/>
-      <c r="Y40" s="307"/>
-      <c r="Z40" s="308"/>
-      <c r="AA40" s="308"/>
-      <c r="AB40" s="308"/>
-      <c r="AC40" s="309"/>
-      <c r="AD40" s="307"/>
-      <c r="AE40" s="308"/>
-      <c r="AF40" s="308"/>
-      <c r="AG40" s="308"/>
-      <c r="AH40" s="309"/>
-      <c r="AI40" s="307"/>
-      <c r="AJ40" s="308"/>
-      <c r="AK40" s="308"/>
-      <c r="AL40" s="308"/>
-      <c r="AM40" s="309"/>
+      <c r="C40" s="235"/>
+      <c r="V40" s="235"/>
+      <c r="Y40" s="245"/>
+      <c r="Z40" s="246"/>
+      <c r="AA40" s="246"/>
+      <c r="AB40" s="246"/>
+      <c r="AC40" s="247"/>
+      <c r="AD40" s="245"/>
+      <c r="AE40" s="246"/>
+      <c r="AF40" s="246"/>
+      <c r="AG40" s="246"/>
+      <c r="AH40" s="247"/>
+      <c r="AI40" s="245"/>
+      <c r="AJ40" s="246"/>
+      <c r="AK40" s="246"/>
+      <c r="AL40" s="246"/>
+      <c r="AM40" s="247"/>
     </row>
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y42" s="294" t="s">
+      <c r="Y42" s="235" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="296" t="s">
+      <c r="Y43" s="248" t="s">
         <v>304</v>
       </c>
-      <c r="Z43" s="297"/>
-      <c r="AA43" s="297"/>
-      <c r="AB43" s="297"/>
-      <c r="AC43" s="298"/>
-      <c r="AD43" s="296" t="s">
+      <c r="Z43" s="249"/>
+      <c r="AA43" s="249"/>
+      <c r="AB43" s="249"/>
+      <c r="AC43" s="250"/>
+      <c r="AD43" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="AE43" s="297"/>
-      <c r="AF43" s="297"/>
-      <c r="AG43" s="297"/>
-      <c r="AH43" s="298"/>
-      <c r="AI43" s="296" t="s">
+      <c r="AE43" s="249"/>
+      <c r="AF43" s="249"/>
+      <c r="AG43" s="249"/>
+      <c r="AH43" s="250"/>
+      <c r="AI43" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="AJ43" s="297"/>
-      <c r="AK43" s="297"/>
-      <c r="AL43" s="297"/>
-      <c r="AM43" s="298"/>
+      <c r="AJ43" s="249"/>
+      <c r="AK43" s="249"/>
+      <c r="AL43" s="249"/>
+      <c r="AM43" s="250"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
-      <c r="D44" s="295"/>
-      <c r="E44" s="299"/>
-      <c r="F44" s="295"/>
-      <c r="G44" s="295"/>
-      <c r="H44" s="295"/>
-      <c r="I44" s="295"/>
-      <c r="J44" s="299"/>
-      <c r="K44" s="295"/>
-      <c r="L44" s="295"/>
-      <c r="M44" s="295"/>
-      <c r="N44" s="295"/>
-      <c r="O44" s="299"/>
-      <c r="P44" s="295"/>
-      <c r="Q44" s="295"/>
-      <c r="W44" s="295"/>
-      <c r="X44" s="299"/>
-      <c r="Y44" s="300"/>
-      <c r="Z44" s="301"/>
-      <c r="AA44" s="301"/>
-      <c r="AB44" s="301"/>
-      <c r="AC44" s="302"/>
-      <c r="AD44" s="301"/>
-      <c r="AE44" s="301"/>
-      <c r="AF44" s="301"/>
-      <c r="AG44" s="301"/>
-      <c r="AH44" s="302"/>
-      <c r="AI44" s="300"/>
-      <c r="AJ44" s="301"/>
-      <c r="AK44" s="301"/>
-      <c r="AL44" s="301"/>
-      <c r="AM44" s="302"/>
+      <c r="D44" s="236"/>
+      <c r="E44" s="237"/>
+      <c r="F44" s="236"/>
+      <c r="G44" s="236"/>
+      <c r="H44" s="236"/>
+      <c r="I44" s="236"/>
+      <c r="J44" s="237"/>
+      <c r="K44" s="236"/>
+      <c r="L44" s="236"/>
+      <c r="M44" s="236"/>
+      <c r="N44" s="236"/>
+      <c r="O44" s="237"/>
+      <c r="P44" s="236"/>
+      <c r="Q44" s="236"/>
+      <c r="W44" s="236"/>
+      <c r="X44" s="237"/>
+      <c r="Y44" s="238"/>
+      <c r="Z44" s="239"/>
+      <c r="AA44" s="239"/>
+      <c r="AB44" s="239"/>
+      <c r="AC44" s="240"/>
+      <c r="AD44" s="239"/>
+      <c r="AE44" s="239"/>
+      <c r="AF44" s="239"/>
+      <c r="AG44" s="239"/>
+      <c r="AH44" s="240"/>
+      <c r="AI44" s="238"/>
+      <c r="AJ44" s="239"/>
+      <c r="AK44" s="239"/>
+      <c r="AL44" s="239"/>
+      <c r="AM44" s="240"/>
     </row>
     <row r="45" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y45" s="303"/>
-      <c r="AC45" s="304"/>
-      <c r="AH45" s="304"/>
-      <c r="AI45" s="303"/>
-      <c r="AM45" s="304"/>
+      <c r="Y45" s="241"/>
+      <c r="AC45" s="242"/>
+      <c r="AH45" s="242"/>
+      <c r="AI45" s="241"/>
+      <c r="AM45" s="242"/>
     </row>
     <row r="46" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y46" s="303"/>
-      <c r="Z46" s="295"/>
-      <c r="AA46" s="299" t="s">
+      <c r="Y46" s="241"/>
+      <c r="Z46" s="236"/>
+      <c r="AA46" s="237" t="s">
         <v>311</v>
       </c>
-      <c r="AB46" s="295"/>
-      <c r="AC46" s="305"/>
-      <c r="AD46" s="295"/>
-      <c r="AE46" s="295"/>
-      <c r="AF46" s="299" t="s">
+      <c r="AB46" s="236"/>
+      <c r="AC46" s="243"/>
+      <c r="AD46" s="236"/>
+      <c r="AE46" s="236"/>
+      <c r="AF46" s="237" t="s">
         <v>312</v>
       </c>
-      <c r="AG46" s="295"/>
-      <c r="AH46" s="305"/>
-      <c r="AI46" s="306"/>
-      <c r="AJ46" s="295"/>
-      <c r="AK46" s="299" t="s">
+      <c r="AG46" s="236"/>
+      <c r="AH46" s="243"/>
+      <c r="AI46" s="244"/>
+      <c r="AJ46" s="236"/>
+      <c r="AK46" s="237" t="s">
         <v>313</v>
       </c>
-      <c r="AL46" s="295"/>
-      <c r="AM46" s="305"/>
+      <c r="AL46" s="236"/>
+      <c r="AM46" s="243"/>
     </row>
     <row r="47" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y47" s="303"/>
-      <c r="AC47" s="304"/>
-      <c r="AH47" s="304"/>
-      <c r="AI47" s="303"/>
-      <c r="AM47" s="304"/>
+      <c r="Y47" s="241"/>
+      <c r="AC47" s="242"/>
+      <c r="AH47" s="242"/>
+      <c r="AI47" s="241"/>
+      <c r="AM47" s="242"/>
     </row>
     <row r="48" spans="3:39" ht="13.15" customHeight="1">
-      <c r="C48" s="294"/>
-      <c r="V48" s="294"/>
-      <c r="Y48" s="307"/>
-      <c r="Z48" s="308"/>
-      <c r="AA48" s="308"/>
-      <c r="AB48" s="308"/>
-      <c r="AC48" s="309"/>
-      <c r="AD48" s="308"/>
-      <c r="AE48" s="308"/>
-      <c r="AF48" s="308"/>
-      <c r="AG48" s="308"/>
-      <c r="AH48" s="309"/>
-      <c r="AI48" s="307"/>
-      <c r="AJ48" s="308"/>
-      <c r="AK48" s="308"/>
-      <c r="AL48" s="308"/>
-      <c r="AM48" s="309"/>
+      <c r="C48" s="235"/>
+      <c r="V48" s="235"/>
+      <c r="Y48" s="245"/>
+      <c r="Z48" s="246"/>
+      <c r="AA48" s="246"/>
+      <c r="AB48" s="246"/>
+      <c r="AC48" s="247"/>
+      <c r="AD48" s="246"/>
+      <c r="AE48" s="246"/>
+      <c r="AF48" s="246"/>
+      <c r="AG48" s="246"/>
+      <c r="AH48" s="247"/>
+      <c r="AI48" s="245"/>
+      <c r="AJ48" s="246"/>
+      <c r="AK48" s="246"/>
+      <c r="AL48" s="246"/>
+      <c r="AM48" s="247"/>
     </row>
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y50" s="294" t="s">
+      <c r="Y50" s="235" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="296" t="s">
+      <c r="Y51" s="248" t="s">
         <v>304</v>
       </c>
-      <c r="Z51" s="297"/>
-      <c r="AA51" s="297"/>
-      <c r="AB51" s="297"/>
-      <c r="AC51" s="298"/>
-      <c r="AD51" s="296" t="s">
+      <c r="Z51" s="249"/>
+      <c r="AA51" s="249"/>
+      <c r="AB51" s="249"/>
+      <c r="AC51" s="250"/>
+      <c r="AD51" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="AE51" s="297"/>
-      <c r="AF51" s="297"/>
-      <c r="AG51" s="297"/>
-      <c r="AH51" s="298"/>
-      <c r="AI51" s="296" t="s">
+      <c r="AE51" s="249"/>
+      <c r="AF51" s="249"/>
+      <c r="AG51" s="249"/>
+      <c r="AH51" s="250"/>
+      <c r="AI51" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="AJ51" s="297"/>
-      <c r="AK51" s="297"/>
-      <c r="AL51" s="297"/>
-      <c r="AM51" s="298"/>
+      <c r="AJ51" s="249"/>
+      <c r="AK51" s="249"/>
+      <c r="AL51" s="249"/>
+      <c r="AM51" s="250"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
-      <c r="D52" s="295"/>
-      <c r="E52" s="299"/>
-      <c r="F52" s="295"/>
-      <c r="G52" s="295"/>
-      <c r="H52" s="295"/>
-      <c r="I52" s="295"/>
-      <c r="J52" s="299"/>
-      <c r="K52" s="295"/>
-      <c r="L52" s="295"/>
-      <c r="M52" s="295"/>
-      <c r="N52" s="295"/>
-      <c r="O52" s="299"/>
-      <c r="P52" s="295"/>
-      <c r="Q52" s="295"/>
-      <c r="W52" s="295"/>
-      <c r="X52" s="299"/>
-      <c r="Y52" s="300"/>
-      <c r="Z52" s="301"/>
-      <c r="AA52" s="301"/>
-      <c r="AB52" s="301"/>
-      <c r="AC52" s="302"/>
-      <c r="AD52" s="301"/>
-      <c r="AE52" s="301"/>
-      <c r="AF52" s="301"/>
-      <c r="AG52" s="301"/>
-      <c r="AH52" s="302"/>
-      <c r="AI52" s="300"/>
-      <c r="AJ52" s="301"/>
-      <c r="AK52" s="301"/>
-      <c r="AL52" s="301"/>
-      <c r="AM52" s="302"/>
+      <c r="D52" s="236"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="236"/>
+      <c r="G52" s="236"/>
+      <c r="H52" s="236"/>
+      <c r="I52" s="236"/>
+      <c r="J52" s="237"/>
+      <c r="K52" s="236"/>
+      <c r="L52" s="236"/>
+      <c r="M52" s="236"/>
+      <c r="N52" s="236"/>
+      <c r="O52" s="237"/>
+      <c r="P52" s="236"/>
+      <c r="Q52" s="236"/>
+      <c r="W52" s="236"/>
+      <c r="X52" s="237"/>
+      <c r="Y52" s="238"/>
+      <c r="Z52" s="239"/>
+      <c r="AA52" s="239"/>
+      <c r="AB52" s="239"/>
+      <c r="AC52" s="240"/>
+      <c r="AD52" s="239"/>
+      <c r="AE52" s="239"/>
+      <c r="AF52" s="239"/>
+      <c r="AG52" s="239"/>
+      <c r="AH52" s="240"/>
+      <c r="AI52" s="238"/>
+      <c r="AJ52" s="239"/>
+      <c r="AK52" s="239"/>
+      <c r="AL52" s="239"/>
+      <c r="AM52" s="240"/>
     </row>
     <row r="53" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y53" s="303"/>
-      <c r="AC53" s="304"/>
-      <c r="AH53" s="304"/>
-      <c r="AI53" s="303"/>
-      <c r="AM53" s="304"/>
+      <c r="Y53" s="241"/>
+      <c r="AC53" s="242"/>
+      <c r="AH53" s="242"/>
+      <c r="AI53" s="241"/>
+      <c r="AM53" s="242"/>
     </row>
     <row r="54" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y54" s="303"/>
-      <c r="Z54" s="295"/>
-      <c r="AA54" s="299" t="s">
+      <c r="Y54" s="241"/>
+      <c r="Z54" s="236"/>
+      <c r="AA54" s="237" t="s">
         <v>315</v>
       </c>
-      <c r="AB54" s="295"/>
-      <c r="AC54" s="305"/>
-      <c r="AD54" s="295"/>
-      <c r="AE54" s="295"/>
-      <c r="AF54" s="299" t="s">
+      <c r="AB54" s="236"/>
+      <c r="AC54" s="243"/>
+      <c r="AD54" s="236"/>
+      <c r="AE54" s="236"/>
+      <c r="AF54" s="237" t="s">
         <v>316</v>
       </c>
-      <c r="AG54" s="295"/>
-      <c r="AH54" s="305"/>
-      <c r="AI54" s="306"/>
-      <c r="AJ54" s="295"/>
-      <c r="AK54" s="299" t="s">
+      <c r="AG54" s="236"/>
+      <c r="AH54" s="243"/>
+      <c r="AI54" s="244"/>
+      <c r="AJ54" s="236"/>
+      <c r="AK54" s="237" t="s">
         <v>309</v>
       </c>
-      <c r="AL54" s="295"/>
-      <c r="AM54" s="305"/>
+      <c r="AL54" s="236"/>
+      <c r="AM54" s="243"/>
     </row>
     <row r="55" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y55" s="303"/>
-      <c r="AC55" s="304"/>
-      <c r="AH55" s="304"/>
-      <c r="AI55" s="303"/>
-      <c r="AM55" s="304"/>
+      <c r="Y55" s="241"/>
+      <c r="AC55" s="242"/>
+      <c r="AH55" s="242"/>
+      <c r="AI55" s="241"/>
+      <c r="AM55" s="242"/>
     </row>
     <row r="56" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y56" s="307"/>
-      <c r="Z56" s="308"/>
-      <c r="AA56" s="308"/>
-      <c r="AB56" s="308"/>
-      <c r="AC56" s="309"/>
-      <c r="AD56" s="308"/>
-      <c r="AE56" s="308"/>
-      <c r="AF56" s="308"/>
-      <c r="AG56" s="308"/>
-      <c r="AH56" s="309"/>
-      <c r="AI56" s="307"/>
-      <c r="AJ56" s="308"/>
-      <c r="AK56" s="308"/>
-      <c r="AL56" s="308"/>
-      <c r="AM56" s="309"/>
+      <c r="Y56" s="245"/>
+      <c r="Z56" s="246"/>
+      <c r="AA56" s="246"/>
+      <c r="AB56" s="246"/>
+      <c r="AC56" s="247"/>
+      <c r="AD56" s="246"/>
+      <c r="AE56" s="246"/>
+      <c r="AF56" s="246"/>
+      <c r="AG56" s="246"/>
+      <c r="AH56" s="247"/>
+      <c r="AI56" s="245"/>
+      <c r="AJ56" s="246"/>
+      <c r="AK56" s="246"/>
+      <c r="AL56" s="246"/>
+      <c r="AM56" s="247"/>
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
-      <c r="AK57" s="291" t="s">
+      <c r="AK57" s="232" t="s">
         <v>317</v>
       </c>
     </row>
@@ -24932,15 +25046,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="10" width="13.08984375" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="13.08984375" customWidth="1"/>
-    <col min="13" max="18" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="10" width="13.125" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="18" width="13.125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -24951,18 +25065,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="238" t="s">
+      <c r="I2" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
+      <c r="J2" s="257"/>
+      <c r="K2" s="257"/>
+      <c r="L2" s="257"/>
+      <c r="M2" s="257"/>
+      <c r="N2" s="257"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="257"/>
+      <c r="Q2" s="257"/>
+      <c r="R2" s="257"/>
     </row>
     <row r="3" spans="2:18" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -24975,18 +25089,18 @@
       <c r="H3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="I3" s="239" t="s">
+      <c r="I3" s="258" t="s">
         <v>168</v>
       </c>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
-      <c r="M3" s="240"/>
-      <c r="N3" s="240"/>
-      <c r="O3" s="240"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
+      <c r="M3" s="259"/>
+      <c r="N3" s="259"/>
+      <c r="O3" s="259"/>
+      <c r="P3" s="259"/>
+      <c r="Q3" s="259"/>
+      <c r="R3" s="259"/>
     </row>
     <row r="4" spans="2:18" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
@@ -25010,34 +25124,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:18" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:18">
-      <c r="C7" s="232" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="233"/>
-      <c r="E7" s="234" t="s">
+      <c r="C7" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="252"/>
+      <c r="E7" s="253" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="234"/>
-      <c r="G7" s="235" t="s">
+      <c r="F7" s="253"/>
+      <c r="G7" s="254" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="235"/>
-      <c r="I7" s="235"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="235"/>
-      <c r="L7" s="235"/>
-      <c r="M7" s="236" t="s">
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="255" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="236"/>
-      <c r="Q7" s="236"/>
-      <c r="R7" s="237"/>
+      <c r="N7" s="255"/>
+      <c r="O7" s="255"/>
+      <c r="P7" s="255"/>
+      <c r="Q7" s="255"/>
+      <c r="R7" s="256"/>
     </row>
-    <row r="8" spans="2:18" ht="26.5" thickBot="1">
+    <row r="8" spans="2:18" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>90</v>
       </c>
@@ -25090,7 +25204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="91.5" thickTop="1">
+    <row r="9" spans="2:18" ht="95.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -25136,7 +25250,7 @@
         <v>44265</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="117">
+    <row r="10" spans="2:18" ht="121.5">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
@@ -25178,7 +25292,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="197"/>
     </row>
-    <row r="11" spans="2:18" ht="130">
+    <row r="11" spans="2:18" ht="135">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -25234,7 +25348,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="197"/>
     </row>
-    <row r="13" spans="2:18" ht="13.5" thickBot="1">
+    <row r="13" spans="2:18" ht="14.25" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -25281,11 +25395,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25299,13 +25413,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="133" t="s">
         <v>127</v>
       </c>
       <c r="C6" s="133"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="67" t="s">
         <v>129</v>
       </c>
@@ -25325,7 +25439,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="143">
         <v>1</v>
       </c>
@@ -25336,7 +25450,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="141"/>
       <c r="D10" s="78"/>
       <c r="E10" s="5"/>
@@ -25344,14 +25458,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="139"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="134" t="s">
         <v>128</v>
       </c>
       <c r="C12" s="74"/>
       <c r="D12" s="74"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="135"/>
       <c r="C13" s="140" t="s">
         <v>129</v>
@@ -25363,7 +25477,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="137">
         <v>0</v>
       </c>
@@ -25440,17 +25554,17 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="141"/>
       <c r="D21" s="78"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="133" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="140" t="s">
         <v>129</v>
       </c>
@@ -25472,7 +25586,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120.25" customHeight="1">
+    <row r="27" spans="2:5" ht="120.2" customHeight="1">
       <c r="C27" s="138">
         <v>1</v>
       </c>
@@ -25537,26 +25651,26 @@
       <c r="D33" s="77"/>
       <c r="E33" s="64"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="141"/>
       <c r="D34" s="78"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="133" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="241"/>
-      <c r="D38" s="242"/>
+      <c r="C38" s="260"/>
+      <c r="D38" s="261"/>
       <c r="E38" s="100" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="243"/>
-      <c r="D39" s="244"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="262"/>
+      <c r="D39" s="263"/>
       <c r="E39" s="5" t="s">
         <v>117</v>
       </c>
@@ -25585,131 +25699,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="245" t="s">
+      <c r="B2" s="289" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="246"/>
-      <c r="D2" s="251" t="s">
+      <c r="C2" s="290"/>
+      <c r="D2" s="277" t="s">
         <v>300</v>
       </c>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="279"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="247" t="s">
+      <c r="B3" s="264" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="248"/>
-      <c r="D3" s="254" t="s">
+      <c r="C3" s="265"/>
+      <c r="D3" s="280" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256"/>
+      <c r="E3" s="281"/>
+      <c r="F3" s="281"/>
+      <c r="G3" s="281"/>
+      <c r="H3" s="282"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="249" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="275" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="250"/>
-      <c r="D4" s="257" t="str">
+      <c r="C4" s="276"/>
+      <c r="D4" s="283" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_BRKBZ-CSTD-2-00-C-C0.c</v>
       </c>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="259"/>
+      <c r="E4" s="284"/>
+      <c r="F4" s="284"/>
+      <c r="G4" s="284"/>
+      <c r="H4" s="285"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="245" t="s">
+      <c r="B6" s="289" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="246"/>
-      <c r="D6" s="260" t="str">
+      <c r="C6" s="290"/>
+      <c r="D6" s="286" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_BRKBZ</v>
       </c>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
-      <c r="G6" s="261"/>
-      <c r="H6" s="262"/>
+      <c r="E6" s="287"/>
+      <c r="F6" s="287"/>
+      <c r="G6" s="287"/>
+      <c r="H6" s="288"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="247" t="s">
+      <c r="B7" s="264" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="248"/>
-      <c r="D7" s="263">
+      <c r="C7" s="265"/>
+      <c r="D7" s="266">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="264"/>
-      <c r="F7" s="264"/>
-      <c r="G7" s="264"/>
-      <c r="H7" s="265"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
+      <c r="H7" s="268"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="264" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="248"/>
-      <c r="D8" s="263" t="str">
+      <c r="C8" s="265"/>
+      <c r="D8" s="266" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_BRKBZ_MTRX</v>
       </c>
-      <c r="E8" s="264"/>
-      <c r="F8" s="264"/>
-      <c r="G8" s="264"/>
-      <c r="H8" s="265"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
+      <c r="H8" s="268"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="264" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="248"/>
-      <c r="D9" s="266" t="s">
+      <c r="C9" s="265"/>
+      <c r="D9" s="269" t="s">
         <v>230</v>
       </c>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="268"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="270"/>
+      <c r="G9" s="270"/>
+      <c r="H9" s="271"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="249" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="275" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="250"/>
-      <c r="D10" s="269"/>
-      <c r="E10" s="270"/>
-      <c r="F10" s="270"/>
-      <c r="G10" s="270"/>
-      <c r="H10" s="271"/>
+      <c r="C10" s="276"/>
+      <c r="D10" s="272"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="273"/>
+      <c r="G10" s="273"/>
+      <c r="H10" s="274"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="124" t="s">
         <v>32</v>
       </c>
@@ -25744,7 +25858,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="96">
         <v>1</v>
       </c>
@@ -26597,7 +26711,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="87">
         <v>25</v>
       </c>
@@ -26638,22 +26752,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -26696,21 +26810,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>185</v>
       </c>
@@ -26718,7 +26832,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="124" t="s">
         <v>32</v>
       </c>
@@ -26756,7 +26870,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="154">
         <v>0</v>
       </c>
@@ -26784,7 +26898,7 @@
       </c>
       <c r="R4" s="123"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="157">
         <v>1</v>
       </c>
@@ -27312,7 +27426,7 @@
       <c r="Q28" s="128"/>
       <c r="R28" s="103"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="158">
         <v>25</v>
       </c>
@@ -27334,7 +27448,7 @@
       <c r="Q29" s="126"/>
       <c r="R29" s="105"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>186</v>
       </c>
@@ -27342,7 +27456,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="124" t="s">
         <v>32</v>
       </c>
@@ -27374,7 +27488,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="154">
         <v>0</v>
       </c>
@@ -27400,7 +27514,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="157">
         <v>1</v>
       </c>
@@ -27928,7 +28042,7 @@
       <c r="Q58" s="128"/>
       <c r="R58" s="159"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="158">
         <v>25</v>
       </c>
@@ -27979,27 +28093,27 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="36" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="80" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="88" t="s">
         <v>56</v>
       </c>
@@ -28043,7 +28157,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="25"/>
       <c r="C3" s="40" t="s">
         <v>106</v>
@@ -28064,7 +28178,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="98" t="s">
         <v>196</v>
       </c>
@@ -28508,7 +28622,7 @@
       </c>
       <c r="U12" s="28"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="98"/>
       <c r="C13" s="97"/>
       <c r="D13" s="106"/>
@@ -30759,7 +30873,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="42"/>
       <c r="C103" s="43"/>
       <c r="D103" s="104"/>
@@ -30832,18 +30946,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -30859,7 +30973,7 @@
       <c r="B2" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="272" t="s">
+      <c r="C2" s="291" t="s">
         <v>82</v>
       </c>
       <c r="D2" s="47">
@@ -30958,7 +31072,7 @@
       <c r="AI2" s="47">
         <v>0</v>
       </c>
-      <c r="AJ2" s="274" t="s">
+      <c r="AJ2" s="293" t="s">
         <v>49</v>
       </c>
     </row>
@@ -30967,7 +31081,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="273"/>
+      <c r="C3" s="292"/>
       <c r="D3" s="114" t="s">
         <v>59</v>
       </c>
@@ -31046,26 +31160,26 @@
       <c r="AC3" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="AD3" s="283" t="s">
+      <c r="AD3" s="302" t="s">
         <v>239</v>
       </c>
-      <c r="AE3" s="284"/>
-      <c r="AF3" s="280" t="s">
+      <c r="AE3" s="303"/>
+      <c r="AF3" s="299" t="s">
         <v>287</v>
       </c>
-      <c r="AG3" s="281"/>
-      <c r="AH3" s="281"/>
-      <c r="AI3" s="282"/>
-      <c r="AJ3" s="275"/>
+      <c r="AG3" s="300"/>
+      <c r="AH3" s="300"/>
+      <c r="AI3" s="301"/>
+      <c r="AJ3" s="294"/>
       <c r="AR3" s="81" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="276" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="277"/>
+      <c r="B4" s="296"/>
       <c r="C4" s="176"/>
       <c r="D4" s="176"/>
       <c r="E4" s="176"/>
@@ -31109,9 +31223,9 @@
       <c r="AV4" s="70"/>
       <c r="AW4" s="71"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="278"/>
-      <c r="B5" s="279"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="297"/>
+      <c r="B5" s="298"/>
       <c r="C5" s="177"/>
       <c r="D5" s="177"/>
       <c r="E5" s="177"/>
@@ -32626,7 +32740,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="120"/>
       <c r="C17" s="36">
         <f t="shared" si="2"/>
@@ -39102,7 +39216,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN                                                      /* 63 UNKNOWN                                         */</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="45" t="s">
         <v>62</v>
       </c>
@@ -59730,38 +59844,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:CU24"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="67.36328125" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="12" width="30.7265625" customWidth="1"/>
-    <col min="13" max="13" width="26.453125" customWidth="1"/>
-    <col min="14" max="21" width="10.90625" customWidth="1"/>
-    <col min="35" max="38" width="8.90625" customWidth="1"/>
-    <col min="51" max="54" width="8.90625" customWidth="1"/>
-    <col min="101" max="116" width="8.90625" customWidth="1"/>
-    <col min="119" max="119" width="8.90625" customWidth="1"/>
+    <col min="2" max="2" width="67.375" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="12" width="30.75" customWidth="1"/>
+    <col min="13" max="13" width="26.5" customWidth="1"/>
+    <col min="14" max="21" width="10.875" customWidth="1"/>
+    <col min="35" max="38" width="8.875" customWidth="1"/>
+    <col min="51" max="54" width="8.875" customWidth="1"/>
+    <col min="101" max="116" width="8.875" customWidth="1"/>
+    <col min="119" max="119" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:99" ht="14.5" thickBot="1">
+    <row r="2" spans="2:99" ht="15" thickBot="1">
       <c r="B2" s="26" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="2:99" ht="14.5" thickBot="1">
+    <row r="3" spans="2:99" ht="15" thickBot="1">
       <c r="B3" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="285" t="s">
+      <c r="C3" s="304" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="286"/>
-      <c r="E3" s="286"/>
-      <c r="F3" s="286"/>
-      <c r="G3" s="286"/>
-      <c r="H3" s="286"/>
-      <c r="I3" s="286"/>
-      <c r="J3" s="287"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
+      <c r="F3" s="305"/>
+      <c r="G3" s="305"/>
+      <c r="H3" s="305"/>
+      <c r="I3" s="305"/>
+      <c r="J3" s="306"/>
       <c r="K3" s="85"/>
       <c r="L3" s="210"/>
       <c r="M3" s="153"/>
@@ -59798,16 +59912,16 @@
       <c r="B5" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="288" t="s">
+      <c r="C5" s="307" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="289"/>
-      <c r="E5" s="289"/>
-      <c r="F5" s="289"/>
-      <c r="G5" s="289"/>
-      <c r="H5" s="289"/>
-      <c r="I5" s="289"/>
-      <c r="J5" s="289"/>
+      <c r="D5" s="308"/>
+      <c r="E5" s="308"/>
+      <c r="F5" s="308"/>
+      <c r="G5" s="308"/>
+      <c r="H5" s="308"/>
+      <c r="I5" s="308"/>
+      <c r="J5" s="308"/>
       <c r="K5" s="213" t="s">
         <v>232</v>
       </c>
@@ -59871,20 +59985,20 @@
       <c r="P6" s="188"/>
       <c r="Q6" s="123"/>
     </row>
-    <row r="7" spans="2:99" ht="53.15" customHeight="1">
+    <row r="7" spans="2:99" ht="53.1" customHeight="1">
       <c r="B7" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="290" t="s">
+      <c r="C7" s="309" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="289"/>
-      <c r="E7" s="289"/>
-      <c r="F7" s="289"/>
-      <c r="G7" s="289"/>
-      <c r="H7" s="289"/>
-      <c r="I7" s="289"/>
-      <c r="J7" s="289"/>
+      <c r="D7" s="308"/>
+      <c r="E7" s="308"/>
+      <c r="F7" s="308"/>
+      <c r="G7" s="308"/>
+      <c r="H7" s="308"/>
+      <c r="I7" s="308"/>
+      <c r="J7" s="308"/>
       <c r="K7" s="213" t="s">
         <v>240</v>
       </c>
@@ -59897,7 +60011,7 @@
       <c r="P7" s="188"/>
       <c r="Q7" s="123"/>
     </row>
-    <row r="8" spans="2:99" ht="131">
+    <row r="8" spans="2:99" ht="136.5">
       <c r="B8" s="60" t="s">
         <v>231</v>
       </c>
@@ -60668,14 +60782,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="73" t="s">
         <v>83</v>
       </c>
@@ -60685,7 +60799,7 @@
       </c>
       <c r="D2" s="74"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="67" t="s">
         <v>83</v>
       </c>
@@ -60696,7 +60810,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -60707,7 +60821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -60718,7 +60832,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -60729,7 +60843,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -60740,7 +60854,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -60762,7 +60876,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -60773,7 +60887,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -60784,7 +60898,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -60795,7 +60909,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -60806,7 +60920,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -60817,7 +60931,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -60839,7 +60953,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -60850,7 +60964,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -60861,7 +60975,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -60894,7 +61008,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -60905,7 +61019,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -60931,7 +61045,7 @@
       <c r="C26" s="77"/>
       <c r="D26" s="64"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="78"/>
       <c r="D27" s="5"/>
